--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_03_Full_84_Cau/Day_03_Ngan_Hang_Phan_01_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_03_Full_84_Cau/Day_03_Ngan_Hang_Phan_01_21_Cau.xlsx
@@ -908,7 +908,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn mô tả trả lời được cả “tool làm gì” và “khi nào không nên dùng”.</t>
+          <t>Mô tả công cụ tốt phải nêu rõ công cụ làm gì và khi nào không nên dùng: 'Tra trạng thái đơn theo order_id; không dùng để đọc hồ sơ khách hàng' giúp mô hình phân biệt ranh giới chính xác nhất với customer_lookup.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_03_Full_84_Cau/Day_03_Ngan_Hang_Phan_01_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_03_Full_84_Cau/Day_03_Ngan_Hang_Phan_01_21_Cau.xlsx
@@ -670,10 +670,19 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra mọi dữ liệu được tạo trước lần gọi model, không chỉ nhìn vào vòng lặp.
-Phân tích theo nguyên lý thiết kế: Kiểm tra mọi dữ liệu được tạo trước lần gọi model, không chỉ nhìn vào vòng lặp.</t>
+- Chỉ ra vi phạm điều kiện đối chứng thuần túy (1.5 điểm): Phân tích việc chạy `search_flights()` trước làm sai lệch baseline, biến chatbot thành Static RAG và triệt tiêu quyền tự chủ.
+- Đề xuất phương án sửa tối thiểu chuẩn xác (1.5 điểm): Loại bỏ việc gọi `search_flights()`, chỉ truyền prompt hệ thống tiêu chuẩn và câu hỏi người dùng vào `llm(...)`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích các điều kiện bị vi phạm của baseline:
+- Vi phạm tính cô lập của mốc đối chứng (Baseline Purity / Fair Comparison): Baseline chatbot định nghĩa là hệ thống xử lý ngôn ngữ chỉ dựa trên tri thức nội tại của mô hình (Zero-tool / No external context injection). Việc chạy ngầm hàm `facts = search_flights()` trước khi gọi mô hình đã biến chatbot thành một dạng 'Static RAG' (Retrieval-Augmented Generation ẩn), làm sai lệch hoàn toàn ranh giới đối chứng về năng lực tự hành.
+- Vi phạm ranh giới thực thi thời gian thực: Dữ liệu bị ép cứng vào prompt hệ thống một cách tất định trước khi LLM phân tích câu hỏi của người dùng, triệt tiêu khả năng tự quyết định 'khi nào cần gọi tool' và 'tham số gọi tool là gì'.
+2. Cách sửa tối thiểu để tạo đối chứng chuẩn xác (Pure Chatbot Baseline):
+- Loại bỏ hoàn toàn dòng gọi hàm `facts = search_flights()` trước khi gửi prompt.
+- Chỉ truyền trực tiếp system prompt tiêu chuẩn (hướng dẫn phong cách, vai trò) và câu hỏi gốc của người dùng vào hàm `llm(...)` mà không kèm theo bất kỳ dữ liệu tra cứu ngoài luồng nào.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Thiết lập ranh giới đối chứng (Baseline Boundary) là nguyên tắc sống còn khi đo lường ROI của Agent. Nếu baseline bí mật 'bơm' dữ liệu bên ngoài qua RAG hoặc tiền xử lý trước cuộc gọi model, người đánh giá sẽ không thể đo lường chính xác giá trị thặng dư mà vòng lặp ReAct của Agent mang lại so với LLM đơn thuần.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents (Evaluation &amp; Baselines) (https://www.anthropic.com/research/building-effective-agents); Yao, S., et al. (2022). ReAct: Synergizing Reasoning and Acting in Language Models (https://arxiv.org/abs/2210.03629)</t>
         </is>
       </c>
     </row>
@@ -701,10 +710,27 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi trường hợp phải buộc một hành vi khác quan sát được.
-Phân tích theo nguyên lý thiết kế: Mỗi trường hợp phải buộc một hành vi khác quan sát được.</t>
+- Trường hợp 1 - Không cần tool (1.0 điểm): Câu hỏi tri thức chung; chatbot trả lời trôi chảy, agent không gọi tool thừa.
+- Trường hợp 2 - Bắt buộc dùng tool (1.5 điểm): Câu hỏi dữ liệu động; chatbot từ chối, agent gọi đúng tool lịch và thời tiết để trả lời.
+- Trường hợp 3 - Tool gặp lỗi (1.5 điểm): Giả lập lỗi API; chatbot từ chối, agent bắt lỗi, xử lý fallback an toàn và thông báo minh bạch giới hạn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế 3 trường hợp kiểm thử đối sánh (Comparison Test Suite) cho trợ lý thời tiết và lịch trình:
+1. Trường hợp 1: Không cần dữ liệu mới (Static Knowledge / Policy Inquiry)
+- Nội dung truy vấn: 'Mùa thu ở Hà Nội thường kéo dài từ tháng mấy đến tháng mấy và thời tiết có đặc điểm gì nổi bật?'
+- Hành vi mong đợi của Chatbot: Trả lời chính xác, trôi chảy dựa trên tri thức được huấn luyện sẵn (mùa thu thường từ tháng 8 đến tháng 10, trời mát mẻ, ít mưa), độ trễ cực thấp (&lt; 1s), không cần công cụ.
+- Hành vi mong đợi của Agent: Nhận diện câu hỏi thuộc tri thức tĩnh, không kích hoạt tool gọi API thời tiết lãng phí, trả lời trực tiếp tương đương chatbot với độ trễ thấp.
+2. Trường hợp 2: Bắt buộc dùng tool (Dynamic Real-time &amp; Private Data)
+- Nội dung truy vấn: 'Chiều nay tôi có lịch họp nào sau 14h không và lúc đó ngoài trời có mưa để tôi chuẩn bị ô không?'
+- Hành vi mong đợi của Chatbot: Từ chối lịch sự hoặc thừa nhận không có quyền truy cập lịch cá nhân và thời tiết thời gian thực ('Tôi không biết lịch trình của bạn...').
+- Hành vi mong đợi của Agent: Phân rã câu hỏi -&gt; Gọi tool `get_calendar(date='today', start_time='14:00')` -&gt; Gọi tool `get_weather(location='current_city', time='afternoon')` -&gt; Hợp nhất Observation -&gt; Trả lời đầy đủ lịch họp và dự báo mưa.
+3. Trường hợp 3: Tool gặp lỗi (Tool Failure &amp; Resilience Handling)
+- Nội dung truy vấn: 'Kiểm tra xem chuyến bay VN123 của tôi trên lịch chiều nay có bị hoãn do thời tiết không?' (Giả lập: Tool API chuyến bay trả về Timeout 504 Gateway Error).
+- Hành vi mong đợi của Chatbot: Khẳng định không có khả năng kiểm tra trực tiếp trạng thái chuyến bay.
+- Hành vi mong đợi của Agent: Bắt ngoại lệ Timeout từ tool, thực hiện retry có giới hạn (1 lần); khi thất bại, chuyển sang cơ chế fallback an toàn: thông báo cho người dùng biết lịch trình đã ghi nhận nhưng dịch vụ tra cứu trạng thái bay đang gián đoạn, khuyến nghị người dùng kiểm tra lại sau hoặc qua ứng dụng hãng hàng không.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Thiết kế bộ kiểm thử đối sánh đa chiều (Differential Testing). Một bộ test suite chuẩn mực phải cô lập được 3 miền hành vi: năng lực tri thức tĩnh (đo độ trễ và chi phí), năng lực điều phối công cụ tự động (đo giá trị thặng dư của Agent) và năng lực xử lý sự cố biên (đo tính bền bỉ).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Cloud - Testing and Evaluating Generative AI and Agent Systems (https://cloud.google.com/vertex-ai/docs/evaluation); Microsoft Research - AutoGen Benchmarking &amp; Differential Testing (https://arxiv.org/abs/2308.08155)</t>
         </is>
       </c>
     </row>
@@ -732,10 +758,22 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng đổi lĩnh vực; hãy thay đổi sự phụ thuộc vào dữ liệu hoặc hành động khi thực thi.
-Phân tích theo nguyên lý thiết kế: Đừng đổi lĩnh vực; hãy thay đổi sự phụ thuộc vào dữ liệu hoặc hành động khi thực thi.</t>
+- Prompt 1 đo giá trị Agent (1.5 điểm): Giữ nguyên ngữ cảnh tóm tắt nhưng yêu cầu đọc dữ liệu qua URL/tool; chatbot từ chối, agent gọi tool lấy nội dung và tóm tắt.
+- Prompt 2 đo hành vi khi tool lỗi (1.5 điểm): Yêu cầu đọc tệp/nguồn gặp lỗi giả lập; agent bắt lỗi chính xác, không hallucinate, phản hồi an toàn cho người dùng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thay thế 2 prompt tóm tắt bằng 2 prompt mới giữ nguyên lĩnh vực xử lý văn bản:
+- Prompt thay thế 1 (Đo lường giá trị thặng dư của Agent - Live Dynamic Retrieval):
+  + Nội dung: 'Hãy đọc bài viết mới nhất vừa được đăng tải sáng nay tại đường dẫn `https://company-wiki.internal/handbook-v2` và tóm tắt 3 thay đổi quan trọng nhất về chính sách làm việc từ xa.'
+  + Hành vi mong đợi của Chatbot: Từ chối hoặc thông báo không thể truy cập internet/mạng nội bộ để duyệt liên kết.
+  + Hành vi mong đợi của Agent: Gọi tool `fetch_webpage(url='https://company-wiki.internal/handbook-v2')`, nhận nội dung trang HTML trong Observation, sau đó tóm tắt chính xác 3 thay đổi.
+- Prompt thay thế 2 (Đo lường hành vi xử lý khi Tool gặp sự cố - Tool Error Resilience):
+  + Nội dung: 'Hãy tóm tắt tệp tài liệu lưu tại kho lưu trữ `s3://reports/2026-financial-audit.pdf`' (Giả lập: Tool trả về lỗi `FileNotFoundError: Mã tài liệu không tồn tại hoặc đã bị lưu trữ kho lạnh`).
+  + Hành vi mong đợi của Chatbot: Thừa nhận không có quyền truy cập vào đường dẫn hệ thống tệp.
+  + Hành vi mong đợi của Agent: Kích hoạt tool đọc file, bắt mã lỗi 404/FileNotFound trong Observation, không ảo giác ra nội dung tóm tắt bịa đặt, phản hồi thông báo rõ ràng tệp tài liệu không tồn tại trên hệ thống lưu trữ và yêu cầu kiểm tra lại đường dẫn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Đa dạng hóa ràng buộc thực thi (Execution Dependency Variation). Nếu tất cả prompt đều là tóm tắt văn bản cung cấp sẵn trong ngữ cảnh (static in-context summarization), agent không mang lại giá trị nào ngoài việc tăng chi phí. Bằng cách thêm ràng buộc đọc URL động và xử lý file không tồn tại, bộ kiểm thử đo lường được khả năng hành động và cơ chế phòng vệ của Agent.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Yao, S., et al. (2022). ReAct: Synergizing Reasoning and Acting in Language Models (https://arxiv.org/abs/2210.03629); Anthropic - Evaluating Agent Capabilities and Error Handling (https://docs.anthropic.com/en/docs/build-with-claude/tool-use)</t>
         </is>
       </c>
     </row>
@@ -763,10 +801,25 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Định nghĩa đạt từ bằng chứng thực thi, không từ độ trôi chảy.
-Phân tích theo nguyên lý thiết kế: Định nghĩa đạt từ bằng chứng thực thi, không từ độ trôi chảy.</t>
+- Thiết lập dữ liệu kiểm thử và câu hỏi (1.0 điểm): Tạo câu hỏi cụ thể ORD-9924 và trạng thái đối lập (đơn bị hủy) trong mock tool.
+- Phân biệt rõ câu trả lời vẻ ngoài và câu có bằng chứng (1.0 điểm): Nhận diện chatbot bịa văn phong hay ('đang giao') là FAIL, agent dựa vào observation ('đã hủy') là PASS.
+- Tiêu chí đạt dựa trên bằng chứng thực thi (1.0 điểm): Khẳng định điều kiện nghiệm thu bắt buộc phải có log gọi tool và thông tin ánh xạ 100% từ tool payload.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế tình huống đối sánh trạng thái đơn hàng (Ground-Truth Evidence Verification):
+1. Dữ liệu đầu vào và Trạng thái Tool giả lập:
+- Câu hỏi của người dùng: 'Đơn hàng mã số ORD-9924 của tôi hiện đang ở đâu và dự kiến bao giờ giao?'
+- Thiết lập dữ liệu kiểm thử (Mock Database / Tool State):
+  + Trong cơ sở dữ liệu thực tế, đơn ORD-9924 có trạng thái: `status: 'CANCELLED_BY_SELLER'` (Đã bị người bán hủy do hết hàng), `reason: 'Out of stock'`, `updated_at: '2026-10-23T08:00:00Z'`.
+  + Tool `check_order_status(order_id)` trả về chính xác JSON: `{"status": "CANCELLED_BY_SELLER", "notes": "Hàng tồn kho đã hết, tiền hoàn vào ví trong 24h"}`.
+2. Phân biệt hai loại phản hồi và Tiêu chí Đạt (Pass Criteria):
+- 'Câu trả lời nghe có vẻ đúng' (Plausible Hallucination - Chatbot không tool): Chatbot tạo ra một câu trả lời cực kỳ lịch sự, văn phong chuẩn mực CSKH: 'Dạ, đơn hàng ORD-9924 của quý khách đang được đóng gói và vận chuyển bởi đơn vị giao vận, dự kiến sẽ giao tới bạn trong 2-3 ngày tới.' -&gt; KẾT LUẬN: ĐÁNH RỚT (FAIL) vì đây là ảo giác nguy hại, trái ngược hoàn toàn thực tế đơn đã bị hủy.
+- 'Câu trả lời có bằng chứng thực thi' (Evidence-Gated Answer - Agent): Agent gọi tool `check_order_status(order_id='ORD-9924')`, nhận Observation trạng thái 'CANCELLED_BY_SELLER' và phản hồi: 'Đơn hàng ORD-9924 của bạn đã bị hủy bởi nhà bán hàng vào sáng nay do hết hàng tồn kho. Khoản tiền sẽ được hoàn trả tự động trong vòng 24 giờ.' -&gt; KẾT LUẬN: ĐẠT (PASS).
+3. Tiêu chí nghiệm thu hệ thống:
+- 100% các khẳng định về trạng thái đơn hàng bắt buộc phải ánh xạ trực tiếp từ trường dữ liệu trong Observation của tool. Bất kỳ câu trả lời nào suy đoán trạng thái mà không có log gọi tool đều bị tính là không đạt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tiêu chuẩn Bằng chứng Thực thi (Execution Evidence Gating). Trong các bài toán nghiệp vụ, độ trôi chảy ngôn ngữ (fluency) của LLM là con dao hai lưỡi. Một chatbot trả lời mượt mà nhưng sai sự thật gây tổn thất lớn hơn một thông báo từ chối. Hệ thống Agent chỉ được coi là đạt chuẩn khi mọi thông tin đưa ra đều có nguồn gốc truy vết (provenance) từ log thực thi tool.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Lin, S., et al. (2021). TruthfulQA: Measuring How Models Mimic Human Falsehoods (https://arxiv.org/abs/2109.07958); OpenAI - Evaluating Model Grounding and Evidence (https://cookbook.openai.com/examples/evaluation/getting_started_with_evals)</t>
         </is>
       </c>
     </row>
@@ -795,10 +848,29 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách trường hợp agent tạo thêm giá trị khỏi trường hợp chỉ làm tăng chi phí và độ trễ.
-Phân tích theo nguyên lý thiết kế: Tách trường hợp agent tạo thêm giá trị khỏi trường hợp chỉ làm tăng chi phí và độ trễ.</t>
+- Phân tích định lượng chính xác (1.0 điểm): Nêu rõ độ trễ (0.8s vs 3.9s), token/call (1 vs 3 model calls, 2 tool calls), tỷ lệ 28/40 không cần tool.
+- Lập luận từ chối hai thái cực đơn nhất (1.5 điểm): Giải thích rõ tại sao không nên dùng Agent cho 100% (quá chậm, quá đắt) và không thể dùng Chatbot cho 100% (thiếu dữ liệu realtime).
+- Đề xuất kiến trúc phân luồng có điều kiện (1.5 điểm): Kiến trúc phân luồng Intent Router/Fast-Path (Chatbot cho tri thức tĩnh) và Slow-Path (Agent cho realtime).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Khuyến nghị có điều kiện về việc lựa chọn hệ thống (Decision Architecture Recommendation):
+1. Phân tích định lượng dữ liệu đối sánh:
+- Tỷ lệ thành công: Chatbot đạt 34/40 (85.0%); Agent đạt 36/40 (90.0%). Agent chỉ vượt trội hơn đúng 2 lượt (tăng 5.0%).
+- Chi phí tài nguyên &amp; Độ trễ:
+  + Độ trễ trung vị: Chatbot 0.8s vs Agent 3.9s (Agent chậm hơn gần 5 lần, tăng 3.1s).
+  + Số lượng gọi mô hình: Chatbot 1 lần vs Agent 3 lần/lượt (Agent tốn token gấp ~3 lần).
+  + Số lượng gọi công cụ: Agent gọi trung bình 2 tool/lượt.
+- Đặc điểm nghiệp vụ: Có tới 28/40 lượt (70%) hoàn toàn không cần tool mà chỉ cần tri thức tĩnh; 2 lượt agent làm tốt hơn là do bắt buộc phải có dữ liệu thời gian thực.
+2. Khuyến nghị có điều kiện chính thức (Conditional Routing Recommendation):
+- KHÔNG CHỌN giải pháp 'Dùng Agent toàn bộ cho 100% lưu lượng' (Pure Agent Architecture): Điều này sẽ gây lãng phí 300% chi phí token và làm chậm hệ thống gấp 5 lần trên 70% tác vụ thông thường.
+- KHÔNG CHỌN giải pháp 'Dùng Chatbot toàn bộ' (Pure Chatbot): Khiến hệ thống thất bại hoàn toàn ở các truy vấn thời gian thực.
+- GIẢI PHÁP TỐI ƯU BẮT BUỘC: ÁP DỤNG MÔ HÌNH PHÂN LUỒNG HAI TẦNG (Intent Triage / Fast-Path vs Slow-Path):
+  + Tầng Triage (Phân loại ý định siêu nhẹ): Một bộ phân loại rule-based hoặc embedding nhỏ xác định nhu cầu dữ liệu thời gian thực.
+  + Luồng Nhanh (Fast Path - Chatbot đơn lẻ): Tiếp nhận 70% truy vấn không cần tool -&gt; Trả lời trong 0.8s, chi phí 1x.
+  + Luồng Chậm (Slow Path - Agent ReAct): Chỉ kích hoạt khi phát hiện truy vấn cần gọi API thời gian thực -&gt; Đảm bảo độ chính xác 100% cho nhóm tác vụ khó.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tối ưu hóa Pareto giữa Chi phí, Độ trễ và Độ chính xác (Latency-Cost-Accuracy Pareto Optimization). Agent ReAct có chi phí biên (marginal cost) rất đắt đỏ do vòng lặp suy luận - hành động nhiều bước. Người kiến trúc sư hệ thống phải tách bạch các tác vụ để 'công cụ nặng' chỉ được triển khai khi thực sự mang lại giá trị gia tăng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents (Routing Workflows) (https://www.anthropic.com/research/building-effective-agents); Google Cloud - Architecture: Intent Routing Pattern (https://cloud.google.com/architecture)</t>
         </is>
       </c>
     </row>
@@ -827,10 +899,22 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm sự kiện tạo ra chênh lệch có thể quan sát được.
-Phân tích theo nguyên lý thiết kế: Tìm sự kiện tạo ra chênh lệch có thể quan sát được.</t>
+- Chỉ ra nguyên nhân chậm do gọi tool dư thừa và trùng lặp (1.5 điểm): Nhận diện tool thứ 2 lặp lại dữ liệu của tool 1, phân tích hiện tượng over-tooling khi chatbot 0.6s đã trả lời đúng.
+- Đề xuất bước sửa kỹ thuật cụ thể (1.5 điểm): Sửa prompt quy định kiểm tra đủ bằng chứng thì dừng, rà soát mô tả registry tránh trùng lặp công năng, và thêm tầng định tuyến.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định nguyên nhân gốc rễ của sự khác biệt:
+- Chatbot hoàn thành trong 0.6 giây vì chỉ gọi model một lần duy nhất dựa trên tri thức nội tại, không bị phát sinh độ trễ mạng hay chi phí điều phối.
+- Agent mất tới 4.2 giây (chậm hơn 7 lần) do hai nguyên nhân kỹ thuật nghiêm trọng:
+  + Lỗi thiết kế Prompt hoặc Tool Registry gây 'Gọi Tool Dư Thừa' (Redundant Tool Invocation): Agent gọi tool thứ hai nhưng nội dung trả về chỉ lặp lại dữ liệu của tool thứ nhất. Điều này chứng minh mô hình không nhận thức được bằng chứng đã đủ, hoặc mô tả của 2 tool trong registry bị trùng lặp công năng.
+  + Tác vụ thực tế không đòi hỏi dữ liệu động thời gian thực (Over-tooling): Chatbot không có tool vẫn trả lời đúng hoàn toàn, chứng tỏ câu hỏi nằm trong tri thức huấn luyện, việc Agent kích hoạt 2 tool là lãng phí tài nguyên.
+2. Đề xuất các bước sửa chữa bắt buộc trước khi lựa chọn hệ thống:
+- Tinh chỉnh mô tả Tool và Rà soát Registry: Phân định ranh giới độc lập giữa các tool, loại bỏ các tool có chức năng trùng lặp để mô hình không gọi 2 lần cho cùng một mục đích.
+- Bổ sung điều kiện hoàn tất bằng chứng vào Prompt (Evidence Sufficiency Constraint): Yêu cầu agent kiểm tra: 'Nếu Observation của tool trước đã trả lời trọn vẹn câu hỏi, cấm gọi thêm tool và lập tức tổng hợp Final Answer'.
+- Tích hợp bộ lọc Triage phân luồng: Đánh giá trước xem câu hỏi có thuộc tri thức tĩnh hay không trước khi trao quyền cho vòng lặp Agent.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Triệt tiêu Vòng lặp Dư thừa (Loop Thrashing &amp; Redundant Tooling). Một lỗi phổ biến trong hệ thống Agent là mô hình bị 'nghiện gọi tool' (tool obsession) ngay cả khi đã thu thập đủ bằng chứng hoặc khi câu hỏi chỉ là kiến thức phổ thông. Tối ưu hóa mô tả công cụ và thiết lập điều kiện dừng sớm (early stop) giúp giảm độ trễ và chi phí mà không làm giảm chất lượng phản hồi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic - Building Effective Agents (Prompt Engineering for Tool Use) (https://docs.anthropic.com/en/docs/build-with-claude/tool-use); Yao, S., et al. ReAct (Section: Redundant Actions Analysis).</t>
         </is>
       </c>
     </row>
@@ -859,10 +943,25 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đặt các số đo vào bối cảnh rủi ro của tác vụ.
-Phân tích theo nguyên lý thiết kế: Đặt các số đo vào bối cảnh rủi ro của tác vụ.</t>
+- Quyết định cho sản phẩm FAQ rủi ro thấp (1.5 điểm): Chọn A (Chatbot), lập luận dựa trên chi phí rẻ gấp 9 lần (0.01 vs 0.09 USD) và độ trễ nhanh P95 1.2s, sai số chấp nhận được.
+- Quyết định cho tác vụ tuân thủ rủi ro cao (1.5 điểm): Chọn B (Agent), lập luận dựa trên việc giảm khẳng định thiếu bằng chứng từ 7% xuống 1%, chi phí và độ trễ đóng vai trò phí bảo hiểm rủi ro.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Quyết định kiến trúc dựa trên Ma trận Đánh đổi Rủi ro và Chi phí (Risk-Adjusted Decision Matrix):
+1. Đối với sản phẩm FAQ nội bộ rủi ro thấp (Low-Risk FAQ):
+- QUYẾT ĐỊNH: CHỌN HỆ THỐNG A (CHATBOT THUẦN TÚY).
+- Lập luận kỹ thuật &amp; kinh tế:
+  + Chi phí: Hệ thống A có chi phí 0.01 USD/truy vấn, rẻ hơn 9 LẦN so với Hệ thống B (0.09 USD).
+  + Độ trễ: P95 của A là 1.2 giây, nhanh hơn gần 6 LẦN so với P95 của B (6.8 giây), đảm bảo trải nghiệm người dùng tức thì.
+  + Đánh đổi độ chính xác: Độ chính xác của A là 92% (chỉ kém B 1%), và trong môi trường FAQ nội bộ, tỷ lệ 7% lỗi khẳng định thiếu bằng chứng có hậu quả rất thấp, có thể khắc phục bằng nút phản hồi 'Báo cáo câu trả lời sai' mà không gây thiệt hại tài chính hay pháp lý.
+2. Đối với tác vụ kiểm tra tuân thủ rủi ro cao (High-Risk Compliance Verification):
+- QUYẾT ĐỊNH: CHỌN HỆ THỐNG B (AGENT CÓ BẰNG CHỨNG).
+- Lập luận kỹ thuật &amp; an toàn:
+  + Giảm thiểu rủi ro thảm họa: Hệ thống B kéo tỷ lệ khẳng định thiếu bằng chứng (unsupported claims / hallucinations) từ 7% xuống chỉ còn 1% (giảm 85% rủi ro sai sót).
+  + Phân tích chi phí bất cân xứng: Trong nghiệp vụ tuân thủ pháp lý, kiểm toán tài chính hoặc y tế, một sai sót lọt lưới có thể dẫn đến án phạt hàng trăm nghìn USD hoặc đình chỉ hoạt động. Do đó, chi phí thêm 0.08 USD và độ trễ 6.8s là một khoản 'phí bảo hiểm' hoàn toàn xứng đáng và bắt buộc phải đầu tư.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Định giá Rủi ro trong Thiết kế Hệ thống AI (Risk-Weighted Value Attribution). Không có hệ thống nào vượt trội trong mọi hoàn cảnh. Quyết định kỹ thuật chỉ có giá trị khi đặt cạnh hàm tổn thất (Loss Function) của nghiệp vụ. Rủi ro thấp ưu tiên Tốc độ và Chi phí (Throughput &amp; Unit Economics); Rủi ro cao ưu tiên Tính chính xác và Khả năng kiểm toán (Auditability &amp; Risk Mitigation).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST AI 100-1 - Artificial Intelligence Risk Management Framework (https://nvlpubs.nist.gov/nistpubs/ai/nist.ai.100-1.pdf); Google PAIR Guidebook - Balancing Cost, Latency and Criticality (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -937,10 +1036,23 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu bằng động từ và danh từ đối tượng.
-Phân tích theo nguyên lý thiết kế: Bắt đầu bằng động từ và danh từ đối tượng.</t>
+- Đổi tên công cụ chuẩn mực rõ nghĩa (1.0 điểm): Đổi thành `get_employee_profile` (hoặc tương đương) và `get_support_ticket` (hoặc tương đương).
+- Mô tả công cụ hồ sơ nhân viên rõ ràng (1.0 điểm): Nêu rõ mục đích tra cứu nhân sự, các trường trả về và cảnh báo loại trừ không dùng cho ticket.
+- Mô tả công cụ phiếu hỗ trợ rõ ràng (1.0 điểm): Nêu rõ mục đích tra cứu ticket/sự cố, các trường trạng thái và cảnh báo loại trừ không dùng cho nhân sự.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Đổi tên và thiết kế mô tả mục đích chuẩn xác cho 2 công cụ:
+1. Đổi tên `get_record(id)` thành `get_employee_profile(employee_id)`:
+- Tên công cụ chuẩn hóa: `get_employee_profile`
+- Mô tả mục đích (Purpose Description):
+"Tra cứu thông tin hồ sơ nhân sự nội bộ của một nhân viên bằng mã định danh nhân viên (employee_id). Trả về họ tên, phòng ban, chức danh, ngày vào công ty, email nội bộ và trạng thái làm việc hiện tại. Chỉ sử dụng khi người dùng hỏi về thông tin nhân sự, cán bộ công nhân viên; tuyệt đối không dùng để tra cứu sự cố hay phiếu hỗ trợ kỹ thuật."
+2. Đổi tên `fetch_record(id)` thành `get_support_ticket(ticket_id)`:
+- Tên công cụ chuẩn hóa: `get_support_ticket`
+- Mô tả mục đích (Purpose Description):
+"Truy xuất chi tiết một phiếu yêu cầu hỗ trợ kỹ thuật hoặc chăm sóc khách hàng bằng mã số phiếu (ticket_id). Trả về tiêu đề sự cố, người tạo, mức độ ưu tiên (P1-P4), trạng thái xử lý (Open/In-Progress/Resolved) và lịch sử phản hồi. Chỉ sử dụng khi cần kiểm tra tiến độ giải quyết ticket kỹ thuật; tuyệt đối không dùng để tra cứu hồ sơ nhân sự cá nhân."
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc Đặt tên theo Ngữ nghĩa Rõ ràng (Semantic Tool Disambiguation). Những cái tên mơ hồ như `get_record` hay `fetch_record` gây ra sự chồng chéo trong không gian biểu diễn vector của LLM, khiến mô hình chọn nhầm công cụ (tool confusion). Đặt tên theo mẫu 'Động từ hành động + Danh từ đối tượng nghiệp vụ' kèm mô tả chỉ rõ 'phạm vi dùng' và 'phạm vi cấm' giúp loại bỏ triệt để xung đột.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI - Function Calling &amp; Tool Definition Best Practices (https://platform.openai.com/docs/guides/function-calling); Anthropic - Best Practices for Tool Descriptions (https://docs.anthropic.com/en/docs/build-with-claude/tool-use#best-practices-for-tool-definitions)</t>
         </is>
       </c>
     </row>
@@ -1020,10 +1132,45 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Liệt kê các trường trước, rồi thêm ràng buộc cho từng trường và cho toàn bộ đối tượng.
-Phân tích theo nguyên lý thiết kế: Liệt kê các trường trước, rồi thêm ràng buộc cho từng trường và cho toàn bộ đối tượng.</t>
+- Định nghĩa JSON Schema đầy đủ cú pháp và ràng buộc (2.0 điểm): Đúng cú pháp JSON Schema, `value: number`, `from_unit/to_unit: string` với `enum: ['C', 'F']`, `required` đủ 3 trường và `additionalProperties: false`.
+- Ví dụ payload hợp lệ và giải thích (1.0 điểm): Cung cấp payload JSON đúng quy cách và giải thích lý do đạt chuẩn.
+- Ví dụ payload không hợp lệ và phân tích lỗi (1.0 điểm): Cung cấp payload vi phạm kiểu, vi phạm enum hoặc thừa trường và chỉ rõ lỗi theo schema.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. JSON Schema tối thiểu cho tool `convert_temperature`:
+```json
+{
+  "type": "object",
+  "properties": {
+    "value": {
+      "type": "number",
+      "description": "Giá trị nhiệt độ cần chuyển đổi (số thực hoặc số nguyên)"
+    },
+    "from_unit": {
+      "type": "string",
+      "enum": ["C", "F"],
+      "description": "Đơn vị nguồn, chỉ chấp nhận 'C' hoặc 'F'"
+    },
+    "to_unit": {
+      "type": "string",
+      "enum": ["C", "F"],
+      "description": "Đơn vị đích, chỉ chấp nhận 'C' hoặc 'F'"
+    }
+  },
+  "required": ["value", "from_unit", "to_unit"],
+  "additionalProperties": false
+}
+```
+2. Payload hợp lệ và Payload không hợp lệ:
+- Payload hợp lệ (Valid Payload):
+  `{"value": 37.5, "from_unit": "C", "to_unit": "F"}`
+  + Giải thích: Chứa đầy đủ cả 3 trường bắt buộc, `value` là số (37.5), `from_unit` và `to_unit` đều là chuỗi nằm trong enum cho phép ['C', 'F'] và không có trường lạ ngoài schema.
+- Payload không hợp lệ (Invalid Payload):
+  `{"value": "37.5", "from_unit": "Celsius", "to_unit": "F", "rounding": true}`
+  + Giải thích các vi phạm schema: (1) `value` bị sai kiểu dữ liệu (chuỗi thay vì số `number`); (2) `from_unit` vi phạm ràng buộc enum (giá trị 'Celsius' không nằm trong ['C', 'F']); (3) Vi phạm ràng buộc cấm trường lạ (`additionalProperties: false`) do thừa trường `rounding`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Ràng buộc Thực thi Nghiêm ngặt (JSON Schema Validation Boundaries). LLM có xu hướng tự ý thêm các tham số sáng tạo hoặc viết tắt/dài dòng các giá trị quy ước (ví dụ 'Celsius' thay vì 'C'). Việc định nghĩa tường minh `enum`, `required` và đặc biệt là `additionalProperties: false` là chốt chặn quan trọng nhất ở tầng ranh giới để đảm bảo hàm bên dưới không nhận phải dữ liệu rác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+JSON Schema Specification (Draft 7 / 2020-12) (https://json-schema.org/understanding-json-schema/); OpenAI JSON Schema Reference for Structured Outputs (https://platform.openai.com/docs/guides/structured-outputs)</t>
         </is>
       </c>
     </row>
@@ -1053,10 +1200,28 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chỉ dùng schema đã cho; đừng suy trạng thái phòng.
-Phân tích theo nguyên lý thiết kế: Chỉ dùng schema đã cho; đừng suy trạng thái phòng.</t>
+- Chỉ ra lỗi sai kiểu của `room_id` (1.0 điểm): Nhận diện `7` là number thay vì string theo yêu cầu schema.
+- Chỉ ra lỗi sai định dạng `start` (1.0 điểm): Nhận diện thiếu chuẩn ISO-8601 (`T`) và thiếu thông tin múi giờ (`Z` hoặc offset).
+- Chỉ ra lỗi vượt ngưỡng `duration_minutes` (1.0 điểm): Nhận diện 240 phút vượt quá giới hạn tối đa 180 phút.
+- Chỉ ra lỗi mảng rỗng của `attendees` (1.0 điểm): Nhận diện `[]` vi phạm ràng buộc mảng email không rỗng (minItems &gt;= 1).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân tích 4 lỗi schema độc lập trong payload `{"room_id":7,"start":"2026-09-08 09:00","duration_minutes":240,"attendees":[]}`:
+1. Lỗi 1 - Sai kiểu dữ liệu của `room_id` (Type Mismatch):
+- Schema quy định: `room_id` bắt buộc phải là chuỗi (`type: string`).
+- Thực tế trong payload: `room_id` đang nhận giá trị số nguyên `7` (`type: integer`). Sửa chuẩn: `"room_id": "7"` hoặc mã định danh phòng tương ứng.
+2. Lỗi 2 - Vi phạm định dạng ngày giờ ISO-8601 có múi giờ của `start` (Format Violation):
+- Schema quy định: `start` phải tuân thủ chuẩn ISO-8601 kèm thông tin múi giờ rõ ràng (ISO-8601 with timezone offset, ví dụ `format: date-time`).
+- Thực tế trong payload: `"2026-09-08 09:00"` dùng khoảng trắng ngăn cách giữa ngày và giờ (thay vì ký tự `T`), đồng thời hoàn toàn thiếu múi giờ (thiếu `Z` hoặc `+07:00`). Sửa chuẩn: `"2026-09-08T09:00:00+07:00"`.
+3. Lỗi 3 - Vượt quá giá trị tối đa cho phép của `duration_minutes` (Value Range Out of Bounds):
+- Schema quy định: `duration_minutes` là số nguyên trong khoảng từ 15 đến 180 (`minimum: 15, maximum: 180`).
+- Thực tế trong payload: `240` vượt quá giới hạn tối đa cho phép là 180 phút (4 giờ &gt; 3 giờ).
+4. Lỗi 4 - Mảng `attendees` bị rỗng (Array MinItems Constraint Violation):
+- Schema quy định: `attendees` là mảng danh sách email không rỗng (`type: array, minItems: 1`).
+- Thực tế trong payload: `attendees: []` là mảng rỗng (0 phần tử), vi phạm điều kiện tối thiểu ít nhất một người tham gia.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Xác thực Schema Đa Ràng buộc (Multi-constraint Schema Validation). Một payload gọi tool không chỉ cần đúng cấu trúc JSON mà phải thỏa mãn đầy đủ các lớp ràng buộc: kiểu dữ liệu (type), định dạng tiêu chuẩn (format ISO-8601), khoảng giá trị nghiệp vụ (numeric range boundaries) và kích thước tập hợp (array cardinality).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RFC 3339 - Date and Time on the Internet: Timestamps (https://datatracker.ietf.org/doc/html/rfc3339); JSON Schema Validation Specification (https://json-schema.org/draft/2020-12/json-schema-validation)</t>
         </is>
       </c>
     </row>
@@ -1133,10 +1298,39 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng chỉ ghi lỗi; hãy nêu rõ email có thể đã được gửi hay chưa.
-Phân tích theo nguyên lý thiết kế: Đừng chỉ ghi lỗi; hãy nêu rõ email có thể đã được gửi hay chưa.</t>
+- Trường hợp 1 - Gửi thành công (1.0 điểm): Mã trạng thái thành công, khẳng định tác động bên ngoài ĐÃ XẢY RA.
+- Trường hợp 2 - Người nhận không hợp lệ (1.0 điểm): Lỗi tiền kiểm tra (validation), khẳng định tác động bên ngoài CHƯA XẢY RA.
+- Trường hợp 3 - Hết thời gian chờ (1.0 điểm): Lỗi timeout mạng, khẳng định tác động bên ngoài CHƯA XÁC ĐỊNH (INDETERMINATE) và cảnh báo không retry tùy tiện.
+- Trường hợp 4 - Nhà cung cấp từ chối (1.0 điểm): Lỗi từ chối xử lý (rejection), khẳng định tác động bên ngoài CHẮC CHẮN CHƯA XẢY RA.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế đặc tả kết quả chuẩn hóa (Result Contract) cho `send_email` phân biệt rõ ràng 4 trường hợp và trạng thái tác động bên ngoài (External Side-Effect State):
+1. Cấu trúc Schema phản hồi chuẩn hóa:
+```json
+{
+  "success": boolean,
+  "status_code": string,
+  "side_effect_state": "EXECUTED" | "NOT_EXECUTED" | "INDETERMINATE",
+  "message": string,
+  "error_details": object | null
+}
+```
+2. Đặc tả chi tiết 4 trường hợp nghiệp vụ:
+- Trường hợp 1: Gửi thành công (Success)
+  + Payload: `{"success": true, "status_code": "EMAIL_SENT", "side_effect_state": "EXECUTED", "message": "Email đã gửi thành công tới máy chủ người nhận", "error_details": null}`
+  + Tác động bên ngoài: ĐÃ XẢY RA (EXECUTED). Thư đã được chuyển giao thành công cho SMTP server.
+- Trường hợp 2: Người nhận không hợp lệ trước khi gửi (Validation Failure - Client Error)
+  + Payload: `{"success": false, "status_code": "INVALID_RECIPIENT", "side_effect_state": "NOT_EXECUTED", "message": "Địa chỉ email người nhận sai cú pháp hoặc không tồn tại tên miền", "error_details": {"field": "to", "value": "invalid-email"}}`
+  + Tác động bên ngoài: CHẮC CHẮN CHƯA XẢY RA (NOT_EXECUTED). Tiến trình bị chặn ngay tại khâu tiền kiểm định, hoàn toàn chưa có gói tin nào gửi ra ngoài.
+- Trường hợp 3: Nhà cung cấp hết thời gian chờ (Gateway Timeout - Ambiguous State)
+  + Payload: `{"success": false, "status_code": "GATEWAY_TIMEOUT", "side_effect_state": "INDETERMINATE", "message": "Nhà cung cấp dịch vụ email không phản hồi sau 5000ms. Trạng thái gửi chưa xác định", "error_details": {"retryable": true, "requires_status_check": true}}`
+  + Tác động bên ngoài: CHƯA XÁC ĐỊNH (INDETERMINATE / UNKNOWN). Yêu cầu đã được gửi qua mạng nhưng bị đứt kết nối trước khi nhận ACK. Email có thể đã được gửi hoặc chưa; tuyệt đối không tự ý gửi lại nếu không có mã idempotent.
+- Trường hợp 4: Nhà cung cấp từ chối kết nối/xác thực (Provider Rejection - Execution Refusal)
+  + Payload: `{"success": false, "status_code": "PROVIDER_REJECTED", "side_effect_state": "NOT_EXECUTED", "message": "Máy chủ SMTP từ chối xác thực do hết hạn API Key hoặc bị khóa tài khoản", "error_details": {"http_code": 401, "retryable": false}}`
+  + Tác động bên ngoài: CHẮC CHẮN CHƯA XẢY RA (NOT_EXECUTED). Máy chủ bên ngoài từ chối xử lý ngay tại cổng bắt tay, cam kết email chưa được gửi đi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Quản trị Trạng thái Tác động Phụ Phân tán (Distributed Side-Effect State Contract). Trong hệ thống Agent tự hành, sự cố nghiêm trọng nhất xảy ra khi tool gặp Timeout nhưng hệ thống lại xem như 'chưa gửi' và kích hoạt retry mù quáng, dẫn đến việc gửi trùng lặp hàng chục email cho khách hàng (hoặc trừ tiền thẻ nhiều lần). Việc phân định rõ 3 trạng thái tác động (Executed / Not Executed / Indeterminate) là bắt buộc để điều khiển logic thử lại an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Enterprise Integration Patterns - Idempotent Receiver &amp; Guaranteed Delivery (https://www.enterpriseintegrationpatterns.com/patterns/messaging/IdempotentReceiver.html); Google Cloud API Design Guide - Errors &amp; Side Effects (https://cloud.google.com/apis/design/errors)</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1359,28 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi nhánh cần một trường phân biệt và trạng thái của tác động phụ.
-Phân tích theo nguyên lý thiết kế: Mỗi nhánh cần một trường phân biệt và trạng thái của tác động phụ.</t>
+- Sửa đổi đặc tả phân biệt rõ 4 nhánh (1.5 điểm): Thiết kế schema phân biệt thành công, hết hàng (OUT_OF_STOCK), đầu vào sai (INVALID_INPUT) và timeout (TIMEOUT).
+- Giải thích vì sao không được coi timeout là hết hàng (1.5 điểm): Phân tích tác hại mất doanh thu do báo sai khách hàng, và rủi ro tồn kho thực tế đã bị khóa ngầm gây treo hàng lệch sổ sách.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa đổi đặc tả tối thiểu cho tool `reserve_stock`:
+Thay vì trả `null` chung chung, tool phải trả về cấu trúc đối tượng có mã phân loại lỗi rõ ràng:
+```json
+// Nhánh 1: Thành công
+{"success": true, "status": "RESERVED", "reserved_quantity": 2, "side_effect": true}
+// Nhánh 2: Hết hàng trong kho (Business Domain Rejection)
+{"success": false, "status": "OUT_OF_STOCK", "available_quantity": 0, "side_effect": false}
+// Nhánh 3: Đầu vào sai (Validation Client Error)
+{"success": false, "status": "INVALID_INPUT", "error": "Mã sản phẩm không tồn tại", "side_effect": false}
+// Nhánh 4: Hết thời gian chờ (Infrastructure Gateway Timeout)
+{"success": false, "status": "TIMEOUT", "error": "Cơ sở dữ liệu kho không phản hồi sau 3000ms", "side_effect": "UNKNOWN"}
+```
+2. Giải thích vì sao TUYỆT ĐỐI KHÔNG ĐƯỢC COI HẾT THỜI GIAN CHỜ LÀ HẾT HÀNG:
+- Hậu quả nghiệp vụ sai lệch nghiêm trọng: 'Hết hàng' (Out of stock) là một khẳng định thực tế nghiệp vụ mang tính xác thực (Ground Truth Business Fact). Báo cho khách hàng 'hết hàng' khi thực tế kho vẫn còn hàng sẽ làm mất doanh thu, đánh mất khách hàng vào tay đối thủ và phá hủy niềm tin vào sản phẩm.
+- Khác biệt bản chất về tác động phụ (Side-effect Divergence): Khi Timeout xảy ra, hệ quản trị kho có thể ĐÃ THỰC THI khóa tồn kho thành công nhưng phản hồi mạng về bị đứt đoạn. Nếu agent coi là 'hết hàng' và hủy đơn, tồn kho thực tế bị đóng băng (treo kho), dẫn đến thất thoát hàng và sai lệch sổ sách kế toán.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Tách bạch Lỗi Miền Nghiệp vụ và Lỗi Hạ tầng (Domain Errors vs Infrastructure Failures). Trả về `null` cho mọi trường hợp là mẫu hình chống chỉ định (anti-pattern) làm 'mù' vòng lặp của Agent. Khi hạ tầng gặp sự cố mạng (Timeout), hành vi đúng đắn là thử lại có kiểm soát hoặc chuyển sang hàng đợi đối soát, thay vì suy diễn sai trái thành sự kiện nghiệp vụ (hết hàng).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Newman, S. (2021). Building Microservices (2nd ed.) - Chapter 11: Resiliency and Distributed Transactions. O'Reilly Media; Martin Fowler - Circuit Breaker &amp; Fail-Fast (https://martinfowler.com/bliki/CircuitBreaker.html)</t>
         </is>
       </c>
     </row>
@@ -1249,10 +1461,27 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mô phỏng quan hệ phụ thuộc phát sinh lỗi, rồi kiểm tra kết quả trả về và lần gọi tiếp theo.
-Phân tích theo nguyên lý thiết kế: Mô phỏng quan hệ phụ thuộc phát sinh lỗi, rồi kiểm tra kết quả trả về và lần gọi tiếp theo.</t>
+- Thiết lập dữ liệu kiểm thử mock lỗi mạng (1.0 điểm): Sử dụng mock để giả lập phát sinh `ConnectionError` mà không gọi mạng thực tế.
+- Điều kiện xác nhận kết quả chuẩn hóa (1.0 điểm): Bắt ngoại lệ, không làm sập app, trả về cấu trúc lỗi có cờ `retryable`.
+- Chứng minh runtime tiếp tục chạy không cần LLM (1.0 điểm): Kiểm thử tầng harness thực thi tool tạo ra `ToolMessage` hợp lệ mà không tiêu tốn token mô hình.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Kế hoạch kiểm thử cô lập (Isolated Testing Plan) cho `lookup_customer`:
+1. Dữ liệu kiểm thử và Thiết lập Mocking (Test Fixture &amp; Isolation):
+- Không kết nối đến mạng internet hay API khách hàng thực tế; sử dụng thư viện `unittest.mock` để giả lập hàm kết nối mạng tầng thấp (`requests.get` hoặc `httpx.get`).
+- Test case 1 (Giả lập lỗi mạng): Khi gọi hàm với `customer_id='CUST-101'`, mock object tự động `raise requests.exceptions.ConnectionError('Connection refused to customer database')`.
+- Test case 2 (Thành công): Khi gọi với `customer_id='CUST-200'`, mock trả về payload `{"id": "CUST-200", "name": "Nguyen Van A"}`.
+2. Điều kiện xác nhận kết quả (Assertion Criteria):
+- Xác nhận công cụ KHÔNG ĐƯỢC làm sập tiến trình: Lớp thực thi của tool phải bao bọc khối `try...except ConnectionError`.
+- Xác nhận đầu ra chuẩn hóa: Tool trả về đối tượng `{"success": false, "error_type": "CONNECTION_ERROR", "retryable": true, "message": "Lỗi kết nối cơ sở dữ liệu khách hàng"}`.
+- Xác nhận ghi log: Kiểm tra log của hệ thống ghi nhận đúng sự kiện cảnh báo kèm stack trace.
+3. Chứng minh lớp thực thi tiếp tục xử lý mà chưa cần chạy model (Proving Runtime Resilience):
+- Viết bài kiểm tra tích hợp đơn vị (Unit Execution Harness): Truyền lệnh gọi tool giả định vào hàm thực thi `execute_tool_call(call_id='c1', name='lookup_customer', args={'customer_id':'CUST-101'})`.
+- Kiểm tra trạng thái trả về của Runtime Harness: Hàm trả về đối tượng `ToolMessage(tool_call_id='c1', content=...)` hợp lệ sẵn sàng để nối vào lịch sử hội thoại.
+- Toàn bộ quy trình kiểm thử này thực thi trong môi trường test tự động dạng deterministic, thời gian chạy dưới 10ms mà không hề tốn bất kỳ 1 token LLM nào.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Kiểm thử Cô lập và Nguyên lý Fail-Safe (Isolated Deterministic Testing). Một sai lầm phổ biến khi phát triển Agent là chỉ kiểm thử tool bằng cách chạy toàn bộ luồng với LLM. Kiểm thử cô lập bằng mock đảm bảo tầng thực thi bắt trọn mọi ngoại lệ hệ thống và đóng gói thành Observation an toàn, ngăn chặn tình trạng ứng dụng bị chết đột ngột (unhandled exception crash) khi hạ tầng mạng gặp sự cố.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Python Testing Documentation - unittest.mock (https://docs.python.org/3/library/unittest.mock.html); Fowler, M. - Mocks Aren't Stubs (https://martinfowler.com/articles/mocksArentStubs.html)</t>
         </is>
       </c>
     </row>
@@ -1326,10 +1555,43 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tra đúng khóa trong registry trước khi đọc tham số hoặc gọi hàm.
-Phân tích theo nguyên lý thiết kế: Tra đúng khóa trong registry trước khi đọc tham số hoặc gọi hàm.</t>
+- Viết mã giả điều phối tra đúng khóa trong registry (1.0 điểm): Kiểm tra `name in TOOLS`, chỉ dispatch khi đúng tên, cấm đoán ngầm.
+- Observation trả về cho lỗi sai chính tả (1.0 điểm): Trả về nội dung lỗi thông báo tool không tồn tại kèm danh mục hợp lệ.
+- Chứng minh không tự ý chuyển đổi ngầm (1.0 điểm): Lập luận tính tất định của exact match và nguyên tắc an toàn Fail-Closed cấm fuzzy match.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Mã giả điều phối Registry với Allowlist nghiêm ngặt:
+```python
+# 1. Đăng ký Tool Registry tĩnh (Strict Allowlist)
+TOOLS = {
+    "get_weather": handle_get_weather,
+    "get_calendar": handle_get_calendar
+}
+def dispatch_tool_call(tool_call):
+    name = tool_call.get("name")
+    call_id = tool_call.get("call_id")
+    arguments = tool_call.get("arguments", {})
+    # Kiểm tra ranh giới Allowlist: tra đúng khóa chính xác trong từ điển
+    if name not in TOOLS:
+        # Trả về Observation lỗi chuẩn hóa, KHÔNG ĐOÁN TÊN TOOL
+        return {
+            "call_id": call_id,
+            "error": f"Tool '{name}' không tồn tại trong danh mục cho phép. Danh sách hợp lệ: {list(TOOLS.keys())}",
+            "status": "DISPATCH_FAILED"
+        }
+    # Chỉ gọi hàm khi tên nằm trong allowlist
+    tool_func = TOOLS[name]
+    return tool_func(arguments)
+```
+2. Xử lý trường hợp `name='get_wether'` (sai chính tả):
+- Observation được thêm vào trạng thái:
+  `{"role": "tool", "tool_call_id": "c1", "content": "LỖI ĐIỀU PHỐI: Công cụ 'get_wether' không tồn tại trong Registry danh mục cho phép. Các công cụ khả dụng hiện tại: ['get_weather', 'get_calendar']. Vui lòng kiểm tra lại chính tả tên công cụ."}`
+3. Chứng minh hệ thống không ngầm chuyển sang `get_weather` (No Implicit Coercion):
+- Tính tất định của mã: Mã nguồn kiểm tra toán tử thành viên `if name not in TOOLS:` dựa trên phép so sánh chuỗi nhị phân chính xác (Exact String Equality `name == key`). Do `"get_wether" != "get_weather"`, điều kiện nhánh rẽ hoàn toàn vào khối lỗi.
+- Nguyên tắc bảo mật Fail-Closed: Tuyệt đối không dùng thuật toán so khớp mờ (fuzzy matching / Levenshtein distance) ở tầng điều phối. Mọi suy đoán ngầm ở tầng thực thi sẽ tạo ra lỗ hổng bảo mật nghiêm trọng (Confusion Attacks / Shadow Tool Invocations).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc Danh sách Cho phép Khép kín (Closed Allowlist Enforcement). Một lỗ hổng bảo mật phổ biến trong hệ thống Agent là cố gắng 'thông minh hóa' lớp điều phối bằng cách tự động sửa lỗi chính tả. Nếu cho phép tự động chuyển `get_wether` thành `get_weather`, kẻ tấn công có thể khai thác sự tương đồng tên gọi để thực thi các tool nhạy cảm ngoài ý muốn. Hệ thống điều phối an toàn phải luôn 'Fail-Closed' và trả lỗi tường minh về cho mô hình tự nhận thức.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP - Top 10 for LLM Applications: LLM07 Insecure Plugin Design (https://owasp.org/www-project-top-10-for-large-language-model-applications/); Microsoft Security Best Practices for Copilot Plugins</t>
         </is>
       </c>
     </row>
